--- a/rules/CORE-000793/negative/01/data/unit-test-coreid-FB1601-negative.xlsx
+++ b/rules/CORE-000793/negative/01/data/unit-test-coreid-FB1601-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000793\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC989BC-8122-4BE9-B342-AD772DCC337E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F3D780-1FC2-4B6F-96AC-ED69DA641245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="98">
   <si>
     <t>Product</t>
   </si>
@@ -404,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -429,13 +429,17 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,7 +850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="12.7109375" style="2" customWidth="1"/>
@@ -868,7 +872,7 @@
       <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -883,13 +887,13 @@
         <v>97</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -903,46 +907,9 @@
         <v>97</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1250,16 +1217,14 @@
       <c r="K5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="L5" s="11"/>
       <c r="M5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="10"/>
+      <c r="O5" s="13"/>
       <c r="Q5" s="5">
         <v>151</v>
       </c>
@@ -1304,12 +1269,13 @@
       <c r="K6" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="9" t="s">
         <v>84</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>84</v>
       </c>
+      <c r="O6" s="14"/>
       <c r="T6" s="5" t="s">
         <v>85</v>
       </c>
@@ -1403,16 +1369,16 @@
       <c r="K8" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="12" t="s">
         <v>93</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="O8" s="12"/>
       <c r="P8" s="7">
         <v>141</v>
       </c>
